--- a/tests/densidadAparente1.xlsx
+++ b/tests/densidadAparente1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
   <si>
     <t xml:space="preserve">DATOS DE DENISIDAD APARENTE</t>
   </si>
@@ -159,7 +159,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -178,6 +178,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -200,37 +204,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -303,7 +307,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -371,9 +375,9 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -397,10 +401,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>1</v>
+        <v>1002</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -423,9 +427,9 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -449,10 +453,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>1004</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>15</v>
@@ -475,9 +479,9 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -497,6 +501,344 @@
       </c>
       <c r="H7" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/tests/densidadAparente1.xlsx
+++ b/tests/densidadAparente1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="13">
   <si>
     <t xml:space="preserve">DATOS DE DENISIDAD APARENTE</t>
   </si>
@@ -49,25 +49,13 @@
     <t xml:space="preserve">secado</t>
   </si>
   <si>
-    <t xml:space="preserve">12.45</t>
-  </si>
-  <si>
     <t xml:space="preserve">25.0</t>
   </si>
   <si>
-    <t xml:space="preserve">12.38</t>
-  </si>
-  <si>
     <t xml:space="preserve">24.9</t>
   </si>
   <si>
-    <t xml:space="preserve">13.02</t>
-  </si>
-  <si>
     <t xml:space="preserve">26.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.97</t>
   </si>
   <si>
     <t xml:space="preserve">25.8</t>
@@ -159,7 +147,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -178,10 +166,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -307,7 +291,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.2"/>
@@ -373,134 +357,134 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1001</v>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>215</v>
+        <v>309</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>209</v>
       </c>
-      <c r="G3" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1002</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
+      <c r="C4" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>1003</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
+      <c r="B5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>241</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>233</v>
+        <v>347</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>227</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>1004</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
+      <c r="C6" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>238</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>231</v>
+        <v>365</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>16</v>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>1005</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
+      <c r="B7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>218</v>
+        <v>310</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -510,49 +494,49 @@
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
+      <c r="C8" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>209</v>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>10</v>
+      <c r="G8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>1007</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
+      <c r="B9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>218</v>
+        <v>330</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -562,49 +546,49 @@
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>13</v>
+      <c r="C10" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>241</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>233</v>
+        <v>350</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>227</v>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>14</v>
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>1009</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>15</v>
+      <c r="B11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>238</v>
+        <v>5</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="G11" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>16</v>
+      <c r="G11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -614,49 +598,49 @@
       <c r="B12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
+      <c r="C12" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>218</v>
+        <v>320</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="G12" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>12</v>
+      <c r="G12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>1010</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>9</v>
+      <c r="C13" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>209</v>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>10</v>
+      <c r="G13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -666,49 +650,49 @@
       <c r="B14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>11</v>
+      <c r="C14" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>218</v>
+        <v>330</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="G14" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>12</v>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>1013</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>13</v>
+      <c r="B15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>241</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>233</v>
+        <v>350</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>227</v>
       </c>
-      <c r="G15" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>14</v>
+      <c r="G15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -718,49 +702,49 @@
       <c r="B16" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>15</v>
+      <c r="C16" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>238</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>231</v>
+        <v>365</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>225</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>242</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>16</v>
+      <c r="G16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>1015</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>11</v>
+      <c r="B17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>218</v>
+        <v>315</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>12</v>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -770,49 +754,49 @@
       <c r="B18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>9</v>
+      <c r="C18" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>226</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>215</v>
+        <v>305</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>209</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>10</v>
+      <c r="G18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>1017</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>11</v>
+      <c r="B19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>218</v>
+        <v>330</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="G19" s="1" t="n">
-        <v>235</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>12</v>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -822,23 +806,283 @@
       <c r="B20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>13</v>
+      <c r="C20" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>241</v>
+        <v>5</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>233</v>
+        <v>350</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>227</v>
       </c>
-      <c r="G20" s="1" t="n">
-        <v>245</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>14</v>
+      <c r="G20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>350</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>365</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>315</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>305</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>350</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
